--- a/event_registration_forms/017_regional_academic_decathlon_tournament_entry_form--event_registration_forms.xlsx
+++ b/event_registration_forms/017_regional_academic_decathlon_tournament_entry_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>school_name_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Team Name</t>
+          <t>Team Name (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>team_leaders_email</t>
+          <t>team_leaders_email_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Team Leader's Email</t>
+          <t>Team Leaders Email 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -959,12 +959,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>team_leaders_phone</t>
+          <t>team_leaders_phone_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Team Leader's Phone</t>
+          <t>Team Leaders Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_date_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
